--- a/data_extactor/batch_10_fa/trimmed/batch_0102_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0102_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | حمل‌ونقل | جغرافیا | مخابرات | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | حمل و نقل | جغرافیا | مخابرات | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید دور | زمان واکنش | هماهنگی چندعضوی | جهت‌یابی فضایی | استحکام ایستا</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | جهت‌گیری فضایی | قدرت ایستا</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | نگهبانان و ماموران حفاظتی | مدیران مدیریت بحران و فوریت‌ها | تکنسین‌های فوریت‌های پزشکی | کارشناسان لجستیک و زنجیره تامین | تکنسین‌های نقشه‌برداری | تکنسین‌های مواد ناریه، مهمات و انفجار</t>
+          <t>ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید دور | زمان واکنش | هماهنگی چندعضوی | استدلال ریاضی | محاسبات عددی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | استدلال ریاضی | توانایی عددی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | نگهبانان و ماموران حفاظتی | مدیران مدیریت بحران و فوریت‌ها | کارشناسان لجستیک و زنجیره تامین | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌های نقشه‌برداری | تکنسین‌های مواد ناریه، مهمات و انفجار</t>
+          <t>ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | مدیران مدیریت بحران و پدافند غیرعامل | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | توجه انتخابی | زمان واکنش | مرتب‌سازی اطلاعات | سرعت ادراک</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | توجه انتخابی | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاهی | تکنسین‌های اویونیک و الکترونیک هوانوردی | مدیران مدیریت بحران و فوریت‌ها | کارشناسان لجستیک و زنجیره تامین | سرپرستان رده‌اول پلیس و کارآگاهان | نگهبانان و ماموران حفاظتی</t>
+          <t>کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | تکنسین‌های اویونیک و الکترونیک پرواز | مدیران مدیریت بحران و پدافند غیرعامل | کارشناسان لجستیک و مدیریت زنجیره تأمین | سرپرستان رده‌اول پلیس و کارآگاهان | نگهبانان و ماموران حراست</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | مکانیک | مخابرات | زبان انگلیسی | حمل‌ونقل | آموزش و تدریس</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | مکانیک | مخابرات | زبان انگلیسی | حمل و نقل | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید دور | زمان واکنش | استقامت | هماهنگی کلی بدن | قدرت تنه</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی دور | زمان عکس‌العمل | استقامت | هماهنگی کلی بدن | قدرت تنه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | آتش‌نشانان | نگهبانان و ماموران حفاظتی | افسران و زندانبانان ندامتگاه‌ها | مدیران مدیریت بحران و فوریت‌ها | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های مواد ناریه، مهمات و انفجار</t>
+          <t>ماموران گشت پلیس و کلانتری | آتش‌نشانان | نگهبانان و ماموران حراست | مأموران زندان و بازداشتگاه | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | مخابرات | پزشکی و دندانپزشکی | آموزش و تدریس | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | مخابرات | پزشکی و دندان‌پزشکی | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید دور | زمان واکنش | استقامت | هماهنگی کلی بدن | قدرت پویا</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی دور | زمان عکس‌العمل | استقامت | هماهنگی کلی بدن | قدرت پویا</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | کارآگاهان و بازرسان جنایی | نگهبانان و ماموران حفاظتی | مدیران مدیریت بحران و فوریت‌ها | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های نقشه‌برداری | تکنسین‌های مواد ناریه، مهمات و انفجار</t>
+          <t>ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان جنایی | نگهبانان و ماموران حراست | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | مخابرات | جغرافیا | زبان انگلیسی | رایانه و الکترونیک | حمل‌ونقل</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | مخابرات | جغرافیا | زبان انگلیسی | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید دور | توجه انتخابی | زمان واکنش | هماهنگی چندعضوی | استقامت</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی دور | توجه انتخابی | زمان عکس‌العمل | هماهنگی چند عضو | استقامت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | آتش‌نشانان | نگهبانان و ماموران حفاظتی | مدیران مدیریت بحران و فوریت‌ها | تکنسین‌های فوریت‌های پزشکی | کارشناسان لجستیک و زنجیره تامین | تکنسین‌های مواد ناریه، مهمات و انفجار</t>
+          <t>ماموران گشت پلیس و کلانتری | آتش‌نشانان | نگهبانان و ماموران حراست | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
